--- a/inst/extdata/csv/updated_names.xlsx
+++ b/inst/extdata/csv/updated_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quirozmoreno.1/Documents/GitHub/PhenolicsDB/inst/extdata/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1B1E91-71A9-0843-8DFB-D2B03206360A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A571AC8-D4CF-2D46-8338-00D1BE4A8153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15340" xr2:uid="{0727AA3E-5902-DD45-8FA7-B133B4407E74}"/>
+    <workbookView xWindow="53340" yWindow="2760" windowWidth="23400" windowHeight="25320" xr2:uid="{0727AA3E-5902-DD45-8FA7-B133B4407E74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>6-Hydroxy-7-methoxycoumarin</t>
   </si>
@@ -524,8 +524,131 @@
     <t>Nomenclature (Link)</t>
   </si>
   <si>
-    <r>
-      <t>3-</t>
+    <t>IUPAC names does not have - connecting phenolics aglycone and glycosides</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Isoscopoletin</t>
+  </si>
+  <si>
+    <t>Isoquercitrin</t>
+  </si>
+  <si>
+    <t>Esculetin</t>
+  </si>
+  <si>
+    <t>Kaempferide</t>
+  </si>
+  <si>
+    <t>Isorhamnetin</t>
+  </si>
+  <si>
+    <t>Tamarixetin</t>
+  </si>
+  <si>
+    <t>Chlorogenic acid</t>
+  </si>
+  <si>
+    <t>Cryptochlorogenic acid</t>
+  </si>
+  <si>
+    <t>Neochlorogenic acid</t>
+  </si>
+  <si>
+    <t>Avicularin</t>
+  </si>
+  <si>
+    <t>Guaijaverin</t>
+  </si>
+  <si>
+    <t>Astragalin</t>
+  </si>
+  <si>
+    <t>Quercitrin</t>
+  </si>
+  <si>
+    <t>Cyanidin 3-Galactoside</t>
+  </si>
+  <si>
+    <t>Quercetin-3-galactoside</t>
+  </si>
+  <si>
+    <t>Quercetin-3-glucoside</t>
+  </si>
+  <si>
+    <t>Saponarin</t>
+  </si>
+  <si>
+    <t>Nictoflorin</t>
+  </si>
+  <si>
+    <t>Eriocitrin</t>
+  </si>
+  <si>
+    <t>Neoeriocitrin</t>
+  </si>
+  <si>
+    <t>Rutin</t>
+  </si>
+  <si>
+    <t>Narcissin</t>
+  </si>
+  <si>
+    <t>Quercetin-3-O-glucuronide</t>
+  </si>
+  <si>
+    <r>
+      <t>4prime-</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Methyl kaempferol</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quercetin 3-</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-galactoside</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4'-</t>
     </r>
     <r>
       <rPr>
@@ -548,107 +671,8 @@
     </r>
   </si>
   <si>
-    <t>IUPAC names does not have - connecting phenolics aglycone and glycosides</t>
-  </si>
-  <si>
-    <t>link</t>
-  </si>
-  <si>
-    <t>Isoscopoletin</t>
-  </si>
-  <si>
-    <t>Isoquercitrin</t>
-  </si>
-  <si>
-    <t>Esculetin</t>
-  </si>
-  <si>
-    <t>Kaempferide</t>
-  </si>
-  <si>
-    <t>Isorhamnetin</t>
-  </si>
-  <si>
-    <t>Tamarixetin</t>
-  </si>
-  <si>
-    <t>Chlorogenic acid</t>
-  </si>
-  <si>
-    <t>Cryptochlorogenic acid</t>
-  </si>
-  <si>
-    <t>Neochlorogenic acid</t>
-  </si>
-  <si>
-    <t>Avicularin</t>
-  </si>
-  <si>
-    <t>Guaijaverin</t>
-  </si>
-  <si>
-    <t>Astragalin</t>
-  </si>
-  <si>
-    <t>Quercitrin</t>
-  </si>
-  <si>
-    <t>Cyanidin 3-Galactoside</t>
-  </si>
-  <si>
-    <t>Quercetin-3-galactoside</t>
-  </si>
-  <si>
-    <t>Quercetin-3-glucoside</t>
-  </si>
-  <si>
-    <t>Saponarin</t>
-  </si>
-  <si>
-    <t>Nictoflorin</t>
-  </si>
-  <si>
-    <t>Eriocitrin</t>
-  </si>
-  <si>
-    <t>Neoeriocitrin</t>
-  </si>
-  <si>
-    <t>Rutin</t>
-  </si>
-  <si>
-    <t>Narcissin</t>
-  </si>
-  <si>
-    <t>Quercetin-3-O-glucuronide</t>
-  </si>
-  <si>
-    <r>
-      <t>4prime-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-Methyl kaempferol</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4prime-</t>
+    <r>
+      <t>3'-</t>
     </r>
     <r>
       <rPr>
@@ -671,27 +695,30 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Quercetin 3-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-galactoside</t>
+    <t>Trilobatin</t>
+  </si>
+  <si>
+    <r>
+      <t>phloretin 4'-</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-glucoside</t>
     </r>
   </si>
 </sst>
@@ -699,7 +726,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -747,6 +774,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF212529"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -769,13 +802,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1111,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE87A7C5-AF8E-1040-BA44-A5B231852273}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -1131,7 +1165,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>37</v>
@@ -1171,7 +1205,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>0</v>
@@ -1179,10 +1213,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>42</v>
@@ -1190,15 +1224,15 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>70</v>
@@ -1206,7 +1240,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>32</v>
@@ -1217,7 +1251,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -1225,7 +1259,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>30</v>
@@ -1233,21 +1267,21 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
@@ -1255,7 +1289,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -1263,7 +1297,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
@@ -1271,7 +1305,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1279,7 +1313,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>7</v>
@@ -1287,15 +1321,15 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>11</v>
@@ -1303,7 +1337,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
@@ -1311,7 +1345,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
@@ -1319,7 +1353,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>14</v>
@@ -1327,7 +1361,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>13</v>
@@ -1335,7 +1369,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>17</v>
@@ -1343,7 +1377,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>15</v>
@@ -1351,7 +1385,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>16</v>
@@ -1398,6 +1432,14 @@
       </c>
       <c r="C33" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="23" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/csv/updated_names.xlsx
+++ b/inst/extdata/csv/updated_names.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quirozmoreno.1/Documents/GitHub/PhenolicsDB/inst/extdata/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A571AC8-D4CF-2D46-8338-00D1BE4A8153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C5B945-ABE9-4946-8F80-C3FFBABDDEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53340" yWindow="2760" windowWidth="23400" windowHeight="25320" xr2:uid="{0727AA3E-5902-DD45-8FA7-B133B4407E74}"/>
+    <workbookView xWindow="56300" yWindow="3080" windowWidth="26160" windowHeight="24300" xr2:uid="{0727AA3E-5902-DD45-8FA7-B133B4407E74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>6-Hydroxy-7-methoxycoumarin</t>
   </si>
@@ -600,7 +600,112 @@
   </si>
   <si>
     <r>
-      <t>4prime-</t>
+      <t>Quercetin 3-</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-galactoside</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4'-</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Methyl quercetin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3'-</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Methyl quercetin</t>
+    </r>
+  </si>
+  <si>
+    <t>Trilobatin</t>
+  </si>
+  <si>
+    <r>
+      <t>phloretin 4'-</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-glucoside</t>
+    </r>
+  </si>
+  <si>
+    <t>Phloridzin</t>
+  </si>
+  <si>
+    <t>phloretin 2'-O-glucoside</t>
+  </si>
+  <si>
+    <r>
+      <t>4'-</t>
     </r>
     <r>
       <rPr>
@@ -623,103 +728,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Quercetin 3-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-galactoside</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4'-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-Methyl quercetin</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3'-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-Methyl quercetin</t>
-    </r>
-  </si>
-  <si>
-    <t>Trilobatin</t>
-  </si>
-  <si>
-    <r>
-      <t>phloretin 4'-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-glucoside</t>
-    </r>
+    <t>Herbacetin</t>
+  </si>
+  <si>
+    <t>8-Hydroxykaempferol</t>
+  </si>
+  <si>
+    <t>3-O-methyl Quercetin</t>
+  </si>
+  <si>
+    <t>3'-O-Methyl quercetin</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE87A7C5-AF8E-1040-BA44-A5B231852273}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -1216,7 +1234,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>42</v>
@@ -1227,7 +1245,7 @@
         <v>49</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -1235,7 +1253,7 @@
         <v>50</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -1324,7 +1342,7 @@
         <v>59</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -1436,10 +1454,34 @@
     </row>
     <row r="34" spans="1:3" ht="23" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="3" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>73</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
